--- a/excel/achievementcfg.xlsx
+++ b/excel/achievementcfg.xlsx
@@ -166,7 +166,8 @@
   </si>
   <si>
     <t>任务条件
-格式: 条件id_参数</t>
+格式:
+条件id_参数值_可选参数数组</t>
   </si>
   <si>
     <t xml:space="preserve">任务进度,格式:
@@ -822,12 +823,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1464,7 +1462,7 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1505,7 +1503,6 @@
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4"/>
       <c r="F4">
         <v>1</v>
       </c>
